--- a/DiabetesTracker.xlsx
+++ b/DiabetesTracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://heiway-my.sharepoint.com/personal/evertc02_heiway_net/Documents/Documents/streamlit-and-analytics/my_flask_app/DiabetesTracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1175" documentId="13_ncr:1_{9E831668-67EE-495A-A50A-64C123260486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{011024FA-4555-4093-A2F5-917DAFBF3F1C}"/>
+  <xr:revisionPtr revIDLastSave="1391" documentId="13_ncr:1_{9E831668-67EE-495A-A50A-64C123260486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81198BBA-F398-4628-963E-5188C38523E4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{5319E4B5-F908-47AC-8797-7A3F1E090568}"/>
   </bookViews>
@@ -257,10 +257,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -548,16 +548,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$B$6:$B$101</c:f>
+              <c:f>main!$B$6:$B$130</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>72.400000000000006</c:v>
                 </c:pt>
@@ -844,6 +931,93 @@
                   <c:v>80.599999999999994</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>81.2</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>81.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>82.1</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>81.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>81.3</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>81.3</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>81.3</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>80.8</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>81.7</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>82.1</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>82.9</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>82.1</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>82.6</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>82.2</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>82.1</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>80.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>82.5</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>81.3</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>81.5</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>80.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>80.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>79.5</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>80.2</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>82.1</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>81.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>80.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="124">
                   <c:v>81.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -1142,10 +1316,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -1433,16 +1607,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$C$6:$C$101</c:f>
+              <c:f>main!$C$6:$C$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>14.6</c:v>
                 </c:pt>
@@ -1730,6 +1991,93 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>6.3</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>6.6</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5.9</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>3.9</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>6.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1769,10 +2117,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -2060,16 +2408,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$E$6:$E$101</c:f>
+              <c:f>main!$E$6:$E$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>18.5</c:v>
                 </c:pt>
@@ -2354,6 +2789,93 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>8.4</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>8.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>6.6</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>8.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>11.1</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>9.4</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5.6</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>6.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2393,10 +2915,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -2684,16 +3206,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$G$6:$G$101</c:f>
+              <c:f>main!$G$6:$G$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>16.5</c:v>
                 </c:pt>
@@ -2978,6 +3587,93 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>6.9</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>7.1</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>7.9</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>8.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5.3</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>7.1</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5.9</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>8.4</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>6.3</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>9.6</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>5.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3017,10 +3713,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -3308,16 +4004,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$H$6:$H$101</c:f>
+              <c:f>main!$H$6:$H$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="3">
                   <c:v>14.2</c:v>
                 </c:pt>
@@ -3593,6 +4376,93 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>6.9</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>6.9</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5.3</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>8.4</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>4.3</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>3.9</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>5.6</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3920,10 +4790,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -4211,16 +5081,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$C$6:$C$101</c:f>
+              <c:f>main!$C$6:$C$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>14.6</c:v>
                 </c:pt>
@@ -4508,6 +5465,93 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>6.3</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>6.6</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5.9</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>3.9</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>6.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4795,10 +5839,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -5086,16 +6130,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$E$6:$E$101</c:f>
+              <c:f>main!$E$6:$E$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>18.5</c:v>
                 </c:pt>
@@ -5380,6 +6511,93 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>8.4</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>8.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>6.6</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>8.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>11.1</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>9.4</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5.6</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>6.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5668,10 +6886,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -5959,16 +7177,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$G$6:$G$101</c:f>
+              <c:f>main!$G$6:$G$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>16.5</c:v>
                 </c:pt>
@@ -6253,6 +7558,93 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>6.9</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>7.1</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>7.9</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>8.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5.3</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>7.1</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5.9</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>8.4</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>6.3</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>9.6</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>5.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6551,10 +7943,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -6842,16 +8234,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$H$6:$H$101</c:f>
+              <c:f>main!$H$6:$H$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="3">
                   <c:v>14.2</c:v>
                 </c:pt>
@@ -7127,6 +8606,93 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>6.9</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>6.9</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5.3</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>8.4</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>4.3</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>3.9</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>5.6</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>6.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7448,10 +9014,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -7739,16 +9305,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$I$6:$I$101</c:f>
+              <c:f>main!$I$6:$I$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="12">
                   <c:v>5</c:v>
                 </c:pt>
@@ -7999,6 +9652,93 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="124">
                   <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
@@ -8057,10 +9797,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -8348,16 +10088,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$J$6:$J$101</c:f>
+              <c:f>main!$J$6:$J$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -8644,6 +10471,93 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="124">
                   <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
@@ -8684,10 +10598,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -8975,16 +10889,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$K$6:$K$101</c:f>
+              <c:f>main!$K$6:$K$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -9271,6 +11272,93 @@
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="124">
                   <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
@@ -9647,10 +11735,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -9938,16 +12026,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$F$6:$F$101</c:f>
+              <c:f>main!$F$6:$F$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="12">
                   <c:v>11.1</c:v>
                 </c:pt>
@@ -10196,6 +12371,93 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>9.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>6.4</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>7.2</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>7.6</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>4.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10484,10 +12746,10 @@
           </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>main!$A$6:$A$101</c:f>
+              <c:f>main!$A$6:$A$130</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm\-yy</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="0">
                   <c:v>45463</c:v>
                 </c:pt>
@@ -10775,16 +13037,103 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>45558</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>45559</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>45560</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>45561</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>45562</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>45563</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>45566</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>45567</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>45568</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>45570</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45571</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>45572</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>45573</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>45574</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>45575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>45576</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>45577</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>45579</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>45580</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>45581</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>45582</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>45583</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>45584</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>45585</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>45586</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>45587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>main!$D$6:$D$101</c:f>
+              <c:f>main!$D$6:$D$130</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="125"/>
                 <c:pt idx="12">
                   <c:v>7.8</c:v>
                 </c:pt>
@@ -11036,6 +13385,90 @@
                 </c:pt>
                 <c:pt idx="95" formatCode="0.0">
                   <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="96" formatCode="0.0">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="97" formatCode="0.0">
+                  <c:v>9.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="98" formatCode="0.0">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="99" formatCode="0.0">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="100" formatCode="0.0">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="101" formatCode="0.0">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="102" formatCode="0.0">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="103" formatCode="0.0">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="104" formatCode="0.0">
+                  <c:v>6.8</c:v>
+                </c:pt>
+                <c:pt idx="105" formatCode="0.0">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="106" formatCode="0.0">
+                  <c:v>5.6</c:v>
+                </c:pt>
+                <c:pt idx="107" formatCode="0.0">
+                  <c:v>7.1</c:v>
+                </c:pt>
+                <c:pt idx="108" formatCode="0.0">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="109" formatCode="0.0">
+                  <c:v>7.2</c:v>
+                </c:pt>
+                <c:pt idx="110" formatCode="0.0">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="111" formatCode="0.0">
+                  <c:v>4.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="112" formatCode="0.0">
+                  <c:v>3.8</c:v>
+                </c:pt>
+                <c:pt idx="113" formatCode="0.0">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="114" formatCode="0.0">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="115" formatCode="0.0">
+                  <c:v>3.7</c:v>
+                </c:pt>
+                <c:pt idx="116" formatCode="0.0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="117" formatCode="0.0">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="118" formatCode="0.0">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="119" formatCode="0.0">
+                  <c:v>7.9</c:v>
+                </c:pt>
+                <c:pt idx="120" formatCode="0.0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="121" formatCode="0.0">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="122" formatCode="0.0">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="123" formatCode="0.0">
+                  <c:v>6.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16551,9 +18984,13 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{98229571-E852-4D72-AD88-420739E80AA6}" name="Table2" displayName="Table2" ref="A5:K101" totalsRowShown="0">
-  <autoFilter ref="A5:K101" xr:uid="{98229571-E852-4D72-AD88-420739E80AA6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{98229571-E852-4D72-AD88-420739E80AA6}" name="Table2" displayName="Table2" ref="A5:K130" totalsRowShown="0">
+  <autoFilter ref="A5:K130" xr:uid="{98229571-E852-4D72-AD88-420739E80AA6}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{F3B13052-68BF-4C97-BCA9-A385B988D19D}" name="Date " dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{75CE39A0-3FAC-4324-B899-84EFA5722702}" name="Weight" dataDxfId="1"/>
@@ -16890,7 +19327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44B1A06E-97E0-492A-AFA3-9B50FA5CE61B}">
-  <dimension ref="A1:AD104"/>
+  <dimension ref="A1:AD133"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -16935,32 +19372,32 @@
         <v>7</v>
       </c>
       <c r="B2" s="2">
-        <f>AVERAGE(B6:B132)</f>
-        <v>78.622916666666654</v>
+        <f>AVERAGE(B6:B161)</f>
+        <v>79.289600000000021</v>
       </c>
       <c r="C2" s="2">
-        <f>AVERAGE(C6:C132)</f>
-        <v>6.4572916666666664</v>
+        <f>AVERAGE(C6:C161)</f>
+        <v>6.2280000000000006</v>
       </c>
       <c r="D2" s="2">
-        <f>AVERAGE(D6:D132)</f>
-        <v>5.9815476190476184</v>
+        <f>AVERAGE(D6:D161)</f>
+        <v>5.9352678571428585</v>
       </c>
       <c r="E2" s="2">
-        <f>AVERAGE(E6:E132)</f>
-        <v>7.808421052631572</v>
+        <f>AVERAGE(E6:E161)</f>
+        <v>7.5620967741935443</v>
       </c>
       <c r="F2" s="2">
-        <f>AVERAGE(F6:F132)</f>
-        <v>7.2674698795180754</v>
+        <f>AVERAGE(F6:F161)</f>
+        <v>7.0830357142857148</v>
       </c>
       <c r="G2" s="2">
-        <f>AVERAGE(G6:G132)</f>
-        <v>7.65473684210526</v>
+        <f>AVERAGE(G6:G161)</f>
+        <v>7.3895161290322573</v>
       </c>
       <c r="H2" s="2">
-        <f>AVERAGE(H6:H132)</f>
-        <v>6.6826086956521724</v>
+        <f>AVERAGE(H6:H161)</f>
+        <v>6.5363636363636335</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -16968,32 +19405,32 @@
         <v>8</v>
       </c>
       <c r="B3" s="2">
-        <f>MAX(B6:B139)</f>
-        <v>82.7</v>
+        <f>MAX(B6:B168)</f>
+        <v>82.9</v>
       </c>
       <c r="C3">
-        <f>MIN(C6:C139)</f>
-        <v>4.2</v>
+        <f>MIN(C6:C168)</f>
+        <v>3.5</v>
       </c>
       <c r="D3">
-        <f>MIN(D6:D139)</f>
+        <f>MIN(D6:D168)</f>
+        <v>3.6</v>
+      </c>
+      <c r="E3">
+        <f>MIN(E6:E168)</f>
         <v>3.8</v>
       </c>
-      <c r="E3">
-        <f>MIN(E6:E139)</f>
+      <c r="F3">
+        <f>MIN(F6:F168)</f>
+        <v>3.3</v>
+      </c>
+      <c r="G3">
+        <f>MIN(G6:G168)</f>
         <v>3.8</v>
       </c>
-      <c r="F3">
-        <f>MIN(F6:F139)</f>
-        <v>4.3</v>
-      </c>
-      <c r="G3">
-        <f>MIN(G6:G139)</f>
-        <v>3.8</v>
-      </c>
       <c r="H3">
-        <f>MIN(H6:H139)</f>
-        <v>3.8</v>
+        <f>MIN(H6:H168)</f>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -20009,7 +22446,7 @@
       <c r="J91">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -20045,7 +22482,7 @@
       <c r="J92">
         <v>8</v>
       </c>
-      <c r="K92" s="3">
+      <c r="K92">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -20081,7 +22518,7 @@
       <c r="J93">
         <v>8</v>
       </c>
-      <c r="K93" s="3">
+      <c r="K93">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -20117,7 +22554,7 @@
       <c r="J94">
         <v>0</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>10</v>
       </c>
@@ -20153,7 +22590,7 @@
       <c r="J95">
         <v>8</v>
       </c>
-      <c r="K95" s="3">
+      <c r="K95">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -20189,7 +22626,7 @@
       <c r="J96">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -20225,7 +22662,7 @@
       <c r="J97">
         <v>0</v>
       </c>
-      <c r="K97" s="3">
+      <c r="K97">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>10</v>
       </c>
@@ -20261,7 +22698,7 @@
       <c r="J98">
         <v>8</v>
       </c>
-      <c r="K98" s="3">
+      <c r="K98">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -20297,7 +22734,7 @@
       <c r="J99">
         <v>8</v>
       </c>
-      <c r="K99" s="3">
+      <c r="K99">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -20333,7 +22770,7 @@
       <c r="J100">
         <v>6</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>16</v>
       </c>
@@ -20351,22 +22788,1064 @@
       <c r="D101" s="2">
         <v>7.5</v>
       </c>
+      <c r="E101">
+        <v>8</v>
+      </c>
+      <c r="F101">
+        <v>5.8</v>
+      </c>
+      <c r="G101">
+        <v>5.2</v>
+      </c>
+      <c r="H101">
+        <v>6.9</v>
+      </c>
       <c r="I101">
         <v>10</v>
       </c>
       <c r="J101">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
     </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>45559</v>
+      </c>
+      <c r="B102" s="2">
+        <v>81.400000000000006</v>
+      </c>
+      <c r="C102">
+        <v>4.8</v>
+      </c>
+      <c r="D102" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="E102">
+        <v>8.4</v>
+      </c>
+      <c r="F102">
+        <v>13.5</v>
+      </c>
+      <c r="G102">
+        <v>6.1</v>
+      </c>
+      <c r="H102">
+        <v>6</v>
+      </c>
+      <c r="I102">
+        <v>10</v>
+      </c>
+      <c r="J102">
+        <v>8</v>
+      </c>
+      <c r="K102" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>45560</v>
+      </c>
+      <c r="B103" s="2">
+        <v>82.1</v>
+      </c>
+      <c r="C103">
+        <v>6.6</v>
+      </c>
+      <c r="D103" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E103">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="F103">
+        <v>6.5</v>
+      </c>
+      <c r="G103">
+        <v>7.1</v>
+      </c>
+      <c r="H103">
+        <v>5.3</v>
+      </c>
+      <c r="I103">
+        <v>10</v>
+      </c>
+      <c r="J103">
+        <v>8</v>
+      </c>
+      <c r="K103" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B104" t="s">
+      <c r="A104" s="1">
+        <v>45561</v>
+      </c>
+      <c r="B104" s="2">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="C104">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D104" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E104">
+        <v>7.8</v>
+      </c>
+      <c r="F104">
+        <v>6.4</v>
+      </c>
+      <c r="G104">
+        <v>5.2</v>
+      </c>
+      <c r="H104">
+        <v>5.5</v>
+      </c>
+      <c r="I104">
+        <v>10</v>
+      </c>
+      <c r="J104">
+        <v>8</v>
+      </c>
+      <c r="K104" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>45562</v>
+      </c>
+      <c r="B105" s="2">
+        <v>81.3</v>
+      </c>
+      <c r="C105">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D105" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="E105">
+        <v>6.1</v>
+      </c>
+      <c r="F105">
+        <v>6.1</v>
+      </c>
+      <c r="G105">
+        <v>7.9</v>
+      </c>
+      <c r="H105">
+        <v>5.7</v>
+      </c>
+      <c r="I105">
+        <v>10</v>
+      </c>
+      <c r="J105">
+        <v>8</v>
+      </c>
+      <c r="K105" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>45563</v>
+      </c>
+      <c r="B106" s="2">
+        <v>81.3</v>
+      </c>
+      <c r="C106">
+        <v>5.7</v>
+      </c>
+      <c r="D106" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="E106">
+        <v>6</v>
+      </c>
+      <c r="F106">
+        <v>6</v>
+      </c>
+      <c r="G106">
+        <v>6</v>
+      </c>
+      <c r="H106">
+        <v>7.7</v>
+      </c>
+      <c r="I106">
+        <v>10</v>
+      </c>
+      <c r="J106">
+        <v>8</v>
+      </c>
+      <c r="K106" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>45564</v>
+      </c>
+      <c r="B107" s="2">
+        <v>81.3</v>
+      </c>
+      <c r="C107">
+        <v>6.1</v>
+      </c>
+      <c r="D107" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="E107">
+        <v>8</v>
+      </c>
+      <c r="F107">
+        <v>9</v>
+      </c>
+      <c r="G107">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="H107">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I107">
+        <v>10</v>
+      </c>
+      <c r="J107">
+        <v>8</v>
+      </c>
+      <c r="K107" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>45565</v>
+      </c>
+      <c r="B108" s="2">
+        <v>80.8</v>
+      </c>
+      <c r="C108">
+        <v>5.7</v>
+      </c>
+      <c r="D108" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="E108">
+        <v>7.4</v>
+      </c>
+      <c r="F108">
+        <v>10</v>
+      </c>
+      <c r="G108">
+        <v>6.1</v>
+      </c>
+      <c r="H108">
+        <v>7.3</v>
+      </c>
+      <c r="I108">
+        <v>10</v>
+      </c>
+      <c r="J108">
+        <v>8</v>
+      </c>
+      <c r="K108" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>45566</v>
+      </c>
+      <c r="B109" s="2">
+        <v>81.7</v>
+      </c>
+      <c r="C109">
+        <v>5.8</v>
+      </c>
+      <c r="D109" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="E109">
+        <v>6.6</v>
+      </c>
+      <c r="F109">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G109">
+        <v>5.3</v>
+      </c>
+      <c r="H109">
+        <v>8.5</v>
+      </c>
+      <c r="I109">
+        <v>10</v>
+      </c>
+      <c r="J109">
+        <v>8</v>
+      </c>
+      <c r="K109" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>45567</v>
+      </c>
+      <c r="B110" s="2">
+        <v>82.1</v>
+      </c>
+      <c r="C110">
+        <v>6.8</v>
+      </c>
+      <c r="D110" s="2">
+        <v>6.8</v>
+      </c>
+      <c r="E110">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F110">
+        <v>6</v>
+      </c>
+      <c r="G110">
+        <v>7</v>
+      </c>
+      <c r="H110">
+        <v>8.4</v>
+      </c>
+      <c r="I110">
+        <v>10</v>
+      </c>
+      <c r="J110">
+        <v>8</v>
+      </c>
+      <c r="K110" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>45568</v>
+      </c>
+      <c r="B111" s="2">
+        <v>82.9</v>
+      </c>
+      <c r="C111">
+        <v>5.9</v>
+      </c>
+      <c r="D111" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="E111">
+        <v>7.7</v>
+      </c>
+      <c r="F111">
+        <v>5.2</v>
+      </c>
+      <c r="G111">
+        <v>7.4</v>
+      </c>
+      <c r="H111">
+        <v>4.3</v>
+      </c>
+      <c r="I111">
+        <v>10</v>
+      </c>
+      <c r="J111">
+        <v>8</v>
+      </c>
+      <c r="K111" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>45569</v>
+      </c>
+      <c r="B112" s="2">
+        <v>82.1</v>
+      </c>
+      <c r="C112">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D112" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="E112">
+        <v>6</v>
+      </c>
+      <c r="F112">
+        <v>7.8</v>
+      </c>
+      <c r="G112">
+        <v>9</v>
+      </c>
+      <c r="H112">
+        <v>5.4</v>
+      </c>
+      <c r="I112">
+        <v>10</v>
+      </c>
+      <c r="J112">
+        <v>8</v>
+      </c>
+      <c r="K112" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>45570</v>
+      </c>
+      <c r="B113" s="2">
+        <v>82.6</v>
+      </c>
+      <c r="C113">
+        <v>5.7</v>
+      </c>
+      <c r="D113" s="2">
+        <v>7.1</v>
+      </c>
+      <c r="E113">
+        <v>11.1</v>
+      </c>
+      <c r="F113">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="G113">
+        <v>7.1</v>
+      </c>
+      <c r="H113">
+        <v>5</v>
+      </c>
+      <c r="I113">
+        <v>10</v>
+      </c>
+      <c r="J113">
+        <v>8</v>
+      </c>
+      <c r="K113" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>45571</v>
+      </c>
+      <c r="B114" s="2">
+        <v>82.2</v>
+      </c>
+      <c r="C114">
+        <v>6.4</v>
+      </c>
+      <c r="D114" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="E114">
+        <v>6</v>
+      </c>
+      <c r="F114">
+        <v>6.5</v>
+      </c>
+      <c r="G114">
+        <v>6.2</v>
+      </c>
+      <c r="H114">
+        <v>5.8</v>
+      </c>
+      <c r="I114">
+        <v>10</v>
+      </c>
+      <c r="J114">
+        <v>8</v>
+      </c>
+      <c r="K114" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>45572</v>
+      </c>
+      <c r="B115" s="2">
+        <v>82.1</v>
+      </c>
+      <c r="C115">
+        <v>4.2</v>
+      </c>
+      <c r="D115" s="2">
+        <v>7.2</v>
+      </c>
+      <c r="E115">
+        <v>5.5</v>
+      </c>
+      <c r="F115">
+        <v>6.4</v>
+      </c>
+      <c r="G115">
+        <v>5.2</v>
+      </c>
+      <c r="H115">
+        <v>7.3</v>
+      </c>
+      <c r="I115">
+        <v>10</v>
+      </c>
+      <c r="J115">
+        <v>8</v>
+      </c>
+      <c r="K115" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>45573</v>
+      </c>
+      <c r="B116" s="2">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="C116">
+        <v>5.2</v>
+      </c>
+      <c r="D116" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="E116">
+        <v>6.1</v>
+      </c>
+      <c r="F116">
+        <v>5.4</v>
+      </c>
+      <c r="G116">
+        <v>5.9</v>
+      </c>
+      <c r="H116">
+        <v>5</v>
+      </c>
+      <c r="I116">
+        <v>10</v>
+      </c>
+      <c r="J116">
+        <v>8</v>
+      </c>
+      <c r="K116" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>45574</v>
+      </c>
+      <c r="B117" s="2">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="C117">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D117" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E117">
+        <v>6</v>
+      </c>
+      <c r="F117">
+        <v>5.5</v>
+      </c>
+      <c r="G117">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H117">
+        <v>8</v>
+      </c>
+      <c r="I117">
+        <v>10</v>
+      </c>
+      <c r="J117">
+        <v>8</v>
+      </c>
+      <c r="K117" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>45575</v>
+      </c>
+      <c r="B118" s="2">
+        <v>82.5</v>
+      </c>
+      <c r="C118">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="D118" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="E118">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F118">
+        <v>8.5</v>
+      </c>
+      <c r="G118">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H118">
+        <v>5.5</v>
+      </c>
+      <c r="I118">
+        <v>10</v>
+      </c>
+      <c r="J118">
+        <v>8</v>
+      </c>
+      <c r="K118" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>45576</v>
+      </c>
+      <c r="B119" s="2">
+        <v>81.3</v>
+      </c>
+      <c r="C119">
+        <v>5</v>
+      </c>
+      <c r="D119" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="E119">
+        <v>9.4</v>
+      </c>
+      <c r="F119">
+        <v>3.4</v>
+      </c>
+      <c r="G119">
+        <v>8.4</v>
+      </c>
+      <c r="H119">
+        <v>5</v>
+      </c>
+      <c r="I119">
+        <v>10</v>
+      </c>
+      <c r="J119">
+        <v>8</v>
+      </c>
+      <c r="K119" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>45577</v>
+      </c>
+      <c r="B120" s="2">
+        <v>81.5</v>
+      </c>
+      <c r="C120">
+        <v>3.9</v>
+      </c>
+      <c r="D120" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E120">
+        <v>4.2</v>
+      </c>
+      <c r="F120">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G120">
+        <v>7.7</v>
+      </c>
+      <c r="H120">
+        <v>5</v>
+      </c>
+      <c r="I120">
+        <v>10</v>
+      </c>
+      <c r="J120">
+        <v>8</v>
+      </c>
+      <c r="K120" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>45578</v>
+      </c>
+      <c r="B121" s="2">
+        <v>81</v>
+      </c>
+      <c r="C121">
+        <v>5.7</v>
+      </c>
+      <c r="D121" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="E121">
+        <v>5.6</v>
+      </c>
+      <c r="F121">
+        <v>4.5</v>
+      </c>
+      <c r="G121">
+        <v>5.2</v>
+      </c>
+      <c r="H121">
+        <v>5.8</v>
+      </c>
+      <c r="I121">
+        <v>10</v>
+      </c>
+      <c r="J121">
+        <v>8</v>
+      </c>
+      <c r="K121" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>45579</v>
+      </c>
+      <c r="B122" s="2">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="C122">
+        <v>3.5</v>
+      </c>
+      <c r="D122" s="2">
+        <v>5</v>
+      </c>
+      <c r="E122">
+        <v>5.4</v>
+      </c>
+      <c r="F122">
+        <v>6</v>
+      </c>
+      <c r="G122">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H122">
+        <v>6.7</v>
+      </c>
+      <c r="I122">
+        <v>10</v>
+      </c>
+      <c r="J122">
+        <v>8</v>
+      </c>
+      <c r="K122" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>45580</v>
+      </c>
+      <c r="B123" s="2">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="C123">
+        <v>4.2</v>
+      </c>
+      <c r="D123" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="E123">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F123">
+        <v>7.2</v>
+      </c>
+      <c r="G123">
+        <v>4.8</v>
+      </c>
+      <c r="H123">
+        <v>7</v>
+      </c>
+      <c r="I123">
+        <v>10</v>
+      </c>
+      <c r="J123">
+        <v>8</v>
+      </c>
+      <c r="K123" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>45581</v>
+      </c>
+      <c r="B124" s="2">
+        <v>79.5</v>
+      </c>
+      <c r="C124">
+        <v>5.5</v>
+      </c>
+      <c r="D124" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="E124">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F124">
+        <v>3.3</v>
+      </c>
+      <c r="G124">
+        <v>8</v>
+      </c>
+      <c r="H124">
+        <v>3.9</v>
+      </c>
+      <c r="I124">
+        <v>10</v>
+      </c>
+      <c r="J124">
+        <v>8</v>
+      </c>
+      <c r="K124" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>45582</v>
+      </c>
+      <c r="B125" s="2">
+        <v>80.2</v>
+      </c>
+      <c r="C125">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D125" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="E125">
+        <v>8</v>
+      </c>
+      <c r="F125">
+        <v>8</v>
+      </c>
+      <c r="G125">
+        <v>6.3</v>
+      </c>
+      <c r="H125">
+        <v>3.1</v>
+      </c>
+      <c r="I125">
+        <v>10</v>
+      </c>
+      <c r="J125">
+        <v>8</v>
+      </c>
+      <c r="K125" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>45583</v>
+      </c>
+      <c r="B126" s="2">
+        <v>82.1</v>
+      </c>
+      <c r="C126">
+        <v>5.2</v>
+      </c>
+      <c r="D126" s="2">
+        <v>5</v>
+      </c>
+      <c r="E126">
+        <v>5</v>
+      </c>
+      <c r="F126">
+        <v>6.1</v>
+      </c>
+      <c r="G126">
+        <v>6.7</v>
+      </c>
+      <c r="H126">
+        <v>8</v>
+      </c>
+      <c r="I126">
+        <v>10</v>
+      </c>
+      <c r="J126">
+        <v>8</v>
+      </c>
+      <c r="K126" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>45584</v>
+      </c>
+      <c r="B127" s="2">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="C127">
+        <v>7.3</v>
+      </c>
+      <c r="D127" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="E127">
+        <v>7</v>
+      </c>
+      <c r="F127">
+        <v>7.6</v>
+      </c>
+      <c r="G127">
+        <v>9.6</v>
+      </c>
+      <c r="H127">
+        <v>5.6</v>
+      </c>
+      <c r="I127">
+        <v>10</v>
+      </c>
+      <c r="J127">
+        <v>8</v>
+      </c>
+      <c r="K127" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>45585</v>
+      </c>
+      <c r="B128" s="2">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="C128">
+        <v>7</v>
+      </c>
+      <c r="D128" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="E128">
+        <v>6.5</v>
+      </c>
+      <c r="F128">
+        <v>5.8</v>
+      </c>
+      <c r="G128">
+        <v>7.5</v>
+      </c>
+      <c r="H128">
+        <v>7</v>
+      </c>
+      <c r="I128">
+        <v>10</v>
+      </c>
+      <c r="J128">
+        <v>8</v>
+      </c>
+      <c r="K128" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>45586</v>
+      </c>
+      <c r="B129" s="2">
+        <v>82</v>
+      </c>
+      <c r="C129">
+        <v>6.8</v>
+      </c>
+      <c r="D129" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="E129">
+        <v>6.8</v>
+      </c>
+      <c r="F129">
+        <v>4.8</v>
+      </c>
+      <c r="G129">
+        <v>5.6</v>
+      </c>
+      <c r="H129">
+        <v>6.3</v>
+      </c>
+      <c r="I129">
+        <v>10</v>
+      </c>
+      <c r="J129">
+        <v>8</v>
+      </c>
+      <c r="K129" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>45587</v>
+      </c>
+      <c r="B130" s="2">
+        <v>81.2</v>
+      </c>
+      <c r="C130">
+        <v>6.6</v>
+      </c>
+      <c r="D130" s="2"/>
+      <c r="I130">
+        <v>10</v>
+      </c>
+      <c r="J130">
+        <v>8</v>
+      </c>
+      <c r="K130" s="3">
+        <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B133" t="s">
         <v>13</v>
       </c>
-      <c r="H104" t="s">
+      <c r="H133" t="s">
         <v>2</v>
       </c>
     </row>

--- a/DiabetesTracker.xlsx
+++ b/DiabetesTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://heiway-my.sharepoint.com/personal/evertc02_heiway_net/Documents/Documents/streamlit-and-analytics/my_flask_app/DiabetesTracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1391" documentId="13_ncr:1_{9E831668-67EE-495A-A50A-64C123260486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81198BBA-F398-4628-963E-5188C38523E4}"/>
+  <xr:revisionPtr revIDLastSave="1392" documentId="13_ncr:1_{9E831668-67EE-495A-A50A-64C123260486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBA65C60-2EF8-416D-AA45-50D547B59508}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{5319E4B5-F908-47AC-8797-7A3F1E090568}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>Weight</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>Post Lunch</t>
-  </si>
-  <si>
-    <t>`</t>
   </si>
   <si>
     <t>Daily Insulin</t>
@@ -119,11 +116,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18984,10 +18980,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{98229571-E852-4D72-AD88-420739E80AA6}" name="Table2" displayName="Table2" ref="A5:K130" totalsRowShown="0">
   <autoFilter ref="A5:K130" xr:uid="{98229571-E852-4D72-AD88-420739E80AA6}"/>
@@ -19372,31 +19364,31 @@
         <v>7</v>
       </c>
       <c r="B2" s="2">
-        <f>AVERAGE(B6:B161)</f>
+        <f t="shared" ref="B2:H2" si="0">AVERAGE(B6:B161)</f>
         <v>79.289600000000021</v>
       </c>
       <c r="C2" s="2">
-        <f>AVERAGE(C6:C161)</f>
+        <f t="shared" si="0"/>
         <v>6.2280000000000006</v>
       </c>
       <c r="D2" s="2">
-        <f>AVERAGE(D6:D161)</f>
+        <f t="shared" si="0"/>
         <v>5.9352678571428585</v>
       </c>
       <c r="E2" s="2">
-        <f>AVERAGE(E6:E161)</f>
+        <f t="shared" si="0"/>
         <v>7.5620967741935443</v>
       </c>
       <c r="F2" s="2">
-        <f>AVERAGE(F6:F161)</f>
+        <f t="shared" si="0"/>
         <v>7.0830357142857148</v>
       </c>
       <c r="G2" s="2">
-        <f>AVERAGE(G6:G161)</f>
+        <f t="shared" si="0"/>
         <v>7.3895161290322573</v>
       </c>
       <c r="H2" s="2">
-        <f>AVERAGE(H6:H161)</f>
+        <f t="shared" si="0"/>
         <v>6.5363636363636335</v>
       </c>
     </row>
@@ -19409,27 +19401,27 @@
         <v>82.9</v>
       </c>
       <c r="C3">
-        <f>MIN(C6:C168)</f>
+        <f t="shared" ref="C3:H3" si="1">MIN(C6:C168)</f>
         <v>3.5</v>
       </c>
       <c r="D3">
-        <f>MIN(D6:D168)</f>
+        <f t="shared" si="1"/>
         <v>3.6</v>
       </c>
       <c r="E3">
-        <f>MIN(E6:E168)</f>
+        <f t="shared" si="1"/>
         <v>3.8</v>
       </c>
       <c r="F3">
-        <f>MIN(F6:F168)</f>
+        <f t="shared" si="1"/>
         <v>3.3</v>
       </c>
       <c r="G3">
-        <f>MIN(G6:G168)</f>
+        <f t="shared" si="1"/>
         <v>3.8</v>
       </c>
       <c r="H3">
-        <f>MIN(H6:H168)</f>
+        <f t="shared" si="1"/>
         <v>3.1</v>
       </c>
     </row>
@@ -19465,7 +19457,7 @@
         <v>9</v>
       </c>
       <c r="K5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -22842,7 +22834,7 @@
       <c r="J102">
         <v>8</v>
       </c>
-      <c r="K102" s="3">
+      <c r="K102">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -22878,7 +22870,7 @@
       <c r="J103">
         <v>8</v>
       </c>
-      <c r="K103" s="3">
+      <c r="K103">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -22914,7 +22906,7 @@
       <c r="J104">
         <v>8</v>
       </c>
-      <c r="K104" s="3">
+      <c r="K104">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -22950,7 +22942,7 @@
       <c r="J105">
         <v>8</v>
       </c>
-      <c r="K105" s="3">
+      <c r="K105">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -22986,7 +22978,7 @@
       <c r="J106">
         <v>8</v>
       </c>
-      <c r="K106" s="3">
+      <c r="K106">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23022,7 +23014,7 @@
       <c r="J107">
         <v>8</v>
       </c>
-      <c r="K107" s="3">
+      <c r="K107">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23058,7 +23050,7 @@
       <c r="J108">
         <v>8</v>
       </c>
-      <c r="K108" s="3">
+      <c r="K108">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23094,7 +23086,7 @@
       <c r="J109">
         <v>8</v>
       </c>
-      <c r="K109" s="3">
+      <c r="K109">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23130,7 +23122,7 @@
       <c r="J110">
         <v>8</v>
       </c>
-      <c r="K110" s="3">
+      <c r="K110">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23166,7 +23158,7 @@
       <c r="J111">
         <v>8</v>
       </c>
-      <c r="K111" s="3">
+      <c r="K111">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23202,7 +23194,7 @@
       <c r="J112">
         <v>8</v>
       </c>
-      <c r="K112" s="3">
+      <c r="K112">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23238,7 +23230,7 @@
       <c r="J113">
         <v>8</v>
       </c>
-      <c r="K113" s="3">
+      <c r="K113">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23274,7 +23266,7 @@
       <c r="J114">
         <v>8</v>
       </c>
-      <c r="K114" s="3">
+      <c r="K114">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23310,7 +23302,7 @@
       <c r="J115">
         <v>8</v>
       </c>
-      <c r="K115" s="3">
+      <c r="K115">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23346,7 +23338,7 @@
       <c r="J116">
         <v>8</v>
       </c>
-      <c r="K116" s="3">
+      <c r="K116">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23382,7 +23374,7 @@
       <c r="J117">
         <v>8</v>
       </c>
-      <c r="K117" s="3">
+      <c r="K117">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23418,7 +23410,7 @@
       <c r="J118">
         <v>8</v>
       </c>
-      <c r="K118" s="3">
+      <c r="K118">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23454,7 +23446,7 @@
       <c r="J119">
         <v>8</v>
       </c>
-      <c r="K119" s="3">
+      <c r="K119">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23490,7 +23482,7 @@
       <c r="J120">
         <v>8</v>
       </c>
-      <c r="K120" s="3">
+      <c r="K120">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23526,7 +23518,7 @@
       <c r="J121">
         <v>8</v>
       </c>
-      <c r="K121" s="3">
+      <c r="K121">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23562,7 +23554,7 @@
       <c r="J122">
         <v>8</v>
       </c>
-      <c r="K122" s="3">
+      <c r="K122">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23598,7 +23590,7 @@
       <c r="J123">
         <v>8</v>
       </c>
-      <c r="K123" s="3">
+      <c r="K123">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23634,7 +23626,7 @@
       <c r="J124">
         <v>8</v>
       </c>
-      <c r="K124" s="3">
+      <c r="K124">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23670,7 +23662,7 @@
       <c r="J125">
         <v>8</v>
       </c>
-      <c r="K125" s="3">
+      <c r="K125">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23706,7 +23698,7 @@
       <c r="J126">
         <v>8</v>
       </c>
-      <c r="K126" s="3">
+      <c r="K126">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23742,7 +23734,7 @@
       <c r="J127">
         <v>8</v>
       </c>
-      <c r="K127" s="3">
+      <c r="K127">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23778,7 +23770,7 @@
       <c r="J128">
         <v>8</v>
       </c>
-      <c r="K128" s="3">
+      <c r="K128">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23814,7 +23806,7 @@
       <c r="J129">
         <v>8</v>
       </c>
-      <c r="K129" s="3">
+      <c r="K129">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
@@ -23836,15 +23828,12 @@
       <c r="J130">
         <v>8</v>
       </c>
-      <c r="K130" s="3">
+      <c r="K130">
         <f>SUM(Table2[[#This Row],[Insulin AM]:[Insulin PM]])</f>
         <v>18</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B133" t="s">
-        <v>13</v>
-      </c>
       <c r="H133" t="s">
         <v>2</v>
       </c>
